--- a/12_UAT_traditional/UAT_spreadsheet.xlsx
+++ b/12_UAT_traditional/UAT_spreadsheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python Projects\STQA\stqa_codes\12_UAT_traditional\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEMESTER 7\STQA\stqa_codes\12_UAT_traditional\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51E19FBD-181C-4FA6-92BF-DDC01F1B903E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8AC11E1-2089-4ACA-B690-3C2841F1BA65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9BB84231-8872-4D57-9DF7-1DCB527565BA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{9BB84231-8872-4D57-9DF7-1DCB527565BA}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="62">
   <si>
     <t>Project name</t>
   </si>
@@ -151,6 +151,105 @@
   </si>
   <si>
     <t>Test Steps</t>
+  </si>
+  <si>
+    <t>UAT-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AC-2 </t>
+  </si>
+  <si>
+    <t>Validate pet update</t>
+  </si>
+  <si>
+    <t>1. Open app.
+2. Create "Buddy" with category dog
+3. In form, type ID: 1 and Name: Buddy Jr. (Leave all other fields blank)
+4. Click Update
+5. Click List All Pets.</t>
+  </si>
+  <si>
+    <t>The name of "Buddy" is
+updated to "Buddy Jr."</t>
+  </si>
+  <si>
+    <t>UAT-003</t>
+  </si>
+  <si>
+    <t>Validate pet delete</t>
+  </si>
+  <si>
+    <t>1. Open app
+2. Create "Jokowi" with category dog
+3. Click List All Pets
+4. Click the delete button on "Jokowi"
+5. Jokowi gone</t>
+  </si>
+  <si>
+    <t>The dog "Jokowi" gone</t>
+  </si>
+  <si>
+    <t>UAT-004</t>
+  </si>
+  <si>
+    <t>Validate pet searching</t>
+  </si>
+  <si>
+    <t>1. Open app
+2. Create "Jokowi" with category dog
+3. Click List All Pets
+4. Search for  "Jokowi"
+5. Jokowi appear</t>
+  </si>
+  <si>
+    <t>The dog "Jokowi" appears 
+when searched</t>
+  </si>
+  <si>
+    <t>UAT-005</t>
+  </si>
+  <si>
+    <t>Validate 
+case-insensitive 
+searching</t>
+  </si>
+  <si>
+    <t>1. Open app
+2. Create "Jokowi" with category dog
+3. Click List All Pets
+4. Search for  "jokowi"
+5. Jokowi appear</t>
+  </si>
+  <si>
+    <t>The dog "Jokowi" appears 
+when "jokowi" is searched</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>The dog "Jokowi" didn’t appear
+when searched</t>
+  </si>
+  <si>
+    <t>The dog "Jokowi" didn’t appear
+when "jokowi" is searched</t>
+  </si>
+  <si>
+    <t>The app failed to search for pets</t>
+  </si>
+  <si>
+    <t>nothing happede</t>
+  </si>
+  <si>
+    <t>pets should be returned 
+when searched</t>
+  </si>
+  <si>
+    <t>medium</t>
   </si>
 </sst>
 </file>
@@ -205,7 +304,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -220,6 +319,9 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -536,18 +638,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3D490F1-A528-416A-B9A9-BF8F7C7DE2BF}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="19.77734375" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="23.4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -555,7 +657,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -563,7 +665,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -571,7 +673,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
@@ -579,7 +681,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
@@ -587,12 +689,12 @@
         <v>45973</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
@@ -606,13 +708,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{969B4861-43C6-4039-8EA2-CDF7A91BCA9F}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.109375" customWidth="1"/>
-    <col min="2" max="2" width="30.77734375" customWidth="1"/>
+    <col min="1" max="1" width="6.140625" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>28</v>
       </c>
@@ -620,7 +722,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -628,7 +730,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -636,7 +738,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -644,7 +746,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -652,7 +754,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -667,20 +769,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8E3ECB0-8F53-4674-989C-EF09CE7DAC3B}">
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="4"/>
-    <col min="2" max="2" width="7.33203125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="21.5546875" style="4" customWidth="1"/>
-    <col min="4" max="4" width="32.21875" style="4" customWidth="1"/>
-    <col min="5" max="5" width="24.109375" style="4" customWidth="1"/>
-    <col min="6" max="6" width="24.6640625" style="4" customWidth="1"/>
+    <col min="1" max="1" width="8.85546875" style="4"/>
+    <col min="2" max="2" width="7.28515625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="21.5703125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="32.28515625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="24.140625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="24.7109375" style="4" customWidth="1"/>
     <col min="7" max="7" width="25" style="4" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="4"/>
+    <col min="8" max="16384" width="8.85546875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>12</v>
       </c>
@@ -703,7 +805,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>29</v>
       </c>
@@ -718,6 +820,104 @@
       </c>
       <c r="E2" s="5" t="s">
         <v>31</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="120" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -727,17 +927,17 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA915A5F-4204-4053-8C11-3398D44BF34B}">
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="42.77734375" customWidth="1"/>
-    <col min="4" max="4" width="26.44140625" customWidth="1"/>
-    <col min="5" max="5" width="24.88671875" customWidth="1"/>
-    <col min="6" max="6" width="14.5546875" customWidth="1"/>
-    <col min="7" max="7" width="11.21875" customWidth="1"/>
+    <col min="3" max="3" width="42.7109375" customWidth="1"/>
+    <col min="4" max="4" width="26.42578125" customWidth="1"/>
+    <col min="5" max="5" width="24.85546875" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" customWidth="1"/>
+    <col min="7" max="7" width="11.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>28</v>
       </c>
@@ -757,6 +957,46 @@
         <v>33</v>
       </c>
       <c r="G1" s="2"/>
+    </row>
+    <row r="2" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="E2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="E3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F3" t="s">
+        <v>61</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
